--- a/cert-data/Layered-Security-Certification-OPS-FY26-08.17.2026.xlsx
+++ b/cert-data/Layered-Security-Certification-OPS-FY26-08.17.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konicaminoltanam-my.sharepoint.com/personal/rnesimi_kmbsus_com/Documents/Dashboard Reports/Layered Security Dashboard Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FA6868B-6CAA-47DB-AE59-EDA8CCB57F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B441AE-BB16-4188-AA03-F73303261A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
